--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104695_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104695_W27.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. METU</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5985</v>
+        <v>2.3151</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.007</v>
+        <v>0.4661</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6055</v>
+        <v>1.8489</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7484</v>
+        <v>-0.139</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3838</v>
+        <v>1.4954</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3646</v>
+        <v>-1.6345</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7522</v>
+        <v>0.0323</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0567</v>
+        <v>1.8131</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6955</v>
+        <v>-1.7808</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9962</v>
+        <v>-0.1714</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3271</v>
+        <v>-0.3177</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6691</v>
+        <v>0.1463</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.5367</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9488</v>
+        <v>3.1868</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6547</v>
+        <v>-1.8826</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5686</v>
+        <v>-0.716</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0861</v>
+        <v>-1.1665</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>3.4262</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3461</v>
+        <v>3.4262</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>C. METU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5073</v>
+        <v>1.7357</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3294</v>
+        <v>0.0517</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8368</v>
+        <v>1.6839</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1473</v>
+        <v>3.7296</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4788</v>
+        <v>2.3838</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.626</v>
+        <v>1.3458</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0638</v>
+        <v>2.6956</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8285</v>
+        <v>2.0265</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.7647</v>
+        <v>0.6692</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.211</v>
+        <v>1.034</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3497</v>
+        <v>0.3574</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1387</v>
+        <v>0.6766</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1757</v>
+        <v>2.9592</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.6914</v>
+        <v>-1.49</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5636</v>
+        <v>-0.428</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1278</v>
+        <v>-1.062</v>
       </c>
       <c r="V3" t="n">
-        <v>3.4387</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4387</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.89</v>
+        <v>0.7024</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1457</v>
+        <v>0.2276</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2557</v>
+        <v>0.4748</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3563</v>
+        <v>-0.7183</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1426</v>
+        <v>0.5823</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7864</v>
+        <v>-1.3007</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8532999999999999</v>
+        <v>-1.5375</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6797</v>
+        <v>0.1239</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8264</v>
+        <v>-1.6614</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4971</v>
+        <v>0.8192</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5371</v>
+        <v>0.4584</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04</v>
+        <v>0.3608</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3069</v>
+        <v>-1.332</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3338</v>
+        <v>-0.4138</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0269</v>
+        <v>-0.9182</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.639</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0125</v>
+        <v>-0.3607</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3517</v>
+        <v>0.763</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3391</v>
+        <v>-1.1237</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3594</v>
+        <v>0.0669</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4718</v>
+        <v>0.2068</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8312</v>
+        <v>-0.14</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3001</v>
+        <v>0.6261</v>
       </c>
       <c r="K5" t="n">
-        <v>1.198</v>
+        <v>0.5516</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4981</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0593</v>
+        <v>-0.5592</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7261</v>
+        <v>-0.3447</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3331</v>
+        <v>-0.2144</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8087</v>
+        <v>0.2067</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0374</v>
+        <v>0.137</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2287</v>
+        <v>0.0697</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4783</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.324</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3586</v>
+        <v>-0.0697</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0346</v>
+        <v>-0.5447</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7257</v>
+        <v>-0.5447</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5698</v>
+        <v>-0.1724</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2955</v>
+        <v>-0.3724</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5186</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1314</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.6501</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7929</v>
+        <v>-0.5447</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4383</v>
+        <v>-0.1724</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3546</v>
+        <v>-0.3724</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.3448</v>
+        <v>-0.0697</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0253</v>
+        <v>-0.0697</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3196</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4848</v>
+        <v>-0.7925</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6469</v>
+        <v>0.779</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1317</v>
+        <v>-1.5715</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0665</v>
+        <v>0.3643</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2078</v>
+        <v>1.154</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1413</v>
+        <v>-0.7896</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6288</v>
+        <v>0.8374</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5541</v>
+        <v>1.672</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0746</v>
+        <v>-0.8345</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5622</v>
+        <v>-0.4731</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3463</v>
+        <v>-0.518</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2159</v>
+        <v>0.0449</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0877</v>
+        <v>-0.3845</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0181</v>
+        <v>-0.0097</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0696</v>
+        <v>-0.3747</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6159</v>
+        <v>-1.2137</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0696</v>
+        <v>-0.7834</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5463</v>
+        <v>-0.4304</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5463</v>
+        <v>-1.3585</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1732</v>
+        <v>0.4738</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3732</v>
+        <v>-1.8323</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.3262</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.5048</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5463</v>
+        <v>-1.0323</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1732</v>
+        <v>-0.7048</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3732</v>
+        <v>-0.3275</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0696</v>
+        <v>-0.4275</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0696</v>
+        <v>-0.0702</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.3573</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.4764</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3957</v>
+        <v>-1.3311</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4255</v>
+        <v>-2.0892</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0298</v>
+        <v>0.7581</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1345</v>
+        <v>0.1359</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7849</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6504</v>
+        <v>-0.651</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0922</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0351</v>
+        <v>0.0437</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1237</v>
+        <v>0.1963</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4174</v>
+        <v>-0.0629</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5411</v>
+        <v>0.2592</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3004</v>
+        <v>-3.5015</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1467</v>
+        <v>-3.6346</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1537</v>
+        <v>0.1331</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2239</v>
+        <v>-3.2201</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3552</v>
+        <v>-1.3365</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8687</v>
+        <v>-1.8835</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1596</v>
+        <v>-2.1865</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.066</v>
+        <v>-2.0864</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0643</v>
+        <v>-1.0335</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2615</v>
+        <v>-1.2364</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.4129</v>
+        <v>-1.6261</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2158</v>
+        <v>-0.6741</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1971</v>
+        <v>-0.952</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6606</v>
+        <v>-4.0279</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4502</v>
+        <v>-3.9452</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2104</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0708</v>
+        <v>-2.0663</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2946</v>
+        <v>-2.2757</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2238</v>
+        <v>0.2094</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9479</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3476</v>
+        <v>-1.3552</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3997</v>
+        <v>0.3789</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1229</v>
+        <v>-1.0901</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.947</v>
+        <v>-0.9205</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1362</v>
+        <v>-1.5063</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.234</v>
+        <v>-0.6926</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9022</v>
+        <v>-0.8136</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.773099999999999</v>
+        <v>-7.088599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.642699999999998</v>
+        <v>-8.2347</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8698</v>
+        <v>1.1459</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7677</v>
+        <v>-3.7502</v>
       </c>
       <c r="H12" t="n">
-        <v>3.216499999999999</v>
+        <v>3.298300000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.9843</v>
+        <v>-7.0488</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5285999999999997</v>
+        <v>-0.7428999999999994</v>
       </c>
       <c r="K12" t="n">
-        <v>6.855600000000001</v>
+        <v>6.754900000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.384499999999999</v>
+        <v>-7.4977</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2389</v>
+        <v>-3.007400000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.6391</v>
+        <v>-3.4565</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4002000000000002</v>
+        <v>0.4489999999999998</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.4758</v>
+        <v>-12.5197</v>
       </c>
       <c r="R12" t="n">
-        <v>15.8784</v>
+        <v>15.9343</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.982600000000001</v>
+        <v>-8.315700000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.705</v>
+        <v>-3</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.277699999999999</v>
+        <v>-5.3154</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5748</v>
+        <v>1.5629</v>
       </c>
       <c r="W12" t="n">
-        <v>8.066699999999999</v>
+        <v>8.028200000000002</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.4919</v>
+        <v>-6.4654</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>J. WRIGHT-FOREMAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6214</v>
+        <v>4.9898</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9054</v>
+        <v>4.6276</v>
       </c>
       <c r="F13" t="n">
-        <v>2.716</v>
+        <v>0.3622</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4752</v>
+        <v>3.8774</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2281</v>
+        <v>2.3251</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2471</v>
+        <v>1.5523</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2982</v>
+        <v>3.9625</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5443</v>
+        <v>3.5606</v>
       </c>
       <c r="L13" t="n">
-        <v>1.7539</v>
+        <v>0.4019</v>
       </c>
       <c r="M13" t="n">
-        <v>0.177</v>
+        <v>-0.0851</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3162</v>
+        <v>-1.2355</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4932</v>
+        <v>1.1504</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8929</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2612</v>
+        <v>0.1204</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6317</v>
+        <v>-0.0567</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3856</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3856</v>
+        <v>0.5447</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. WRIGHT-FOREMAN</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2694</v>
+        <v>4.0775</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4341</v>
+        <v>1.6411</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1647</v>
+        <v>2.4363</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9026</v>
+        <v>3.4782</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3539</v>
+        <v>1.221</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5487</v>
+        <v>2.2572</v>
       </c>
       <c r="J14" t="n">
-        <v>4.0057</v>
+        <v>3.2735</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5979</v>
+        <v>1.5233</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4078</v>
+        <v>1.7501</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.103</v>
+        <v>0.2048</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.244</v>
+        <v>-0.3023</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1409</v>
+        <v>0.5071</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5878</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6747</v>
+        <v>2.352</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1179</v>
+        <v>1.0309</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5568</v>
+        <v>1.3211</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5463</v>
+        <v>-0.387</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5463</v>
+        <v>-0.387</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8684</v>
+        <v>1.6661</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5469</v>
+        <v>1.1805</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3215</v>
+        <v>0.4856</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1668</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.1873</v>
+        <v>-0.0116</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0205</v>
+        <v>0.8448</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.0001</v>
+        <v>1.1459</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.1943</v>
+        <v>0.7067</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1941</v>
+        <v>0.4392</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1666</v>
+        <v>-0.3127</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.993</v>
+        <v>-0.7184</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8264</v>
+        <v>0.4057</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>6.3547</v>
+        <v>0.3973</v>
       </c>
       <c r="T15" t="n">
-        <v>5.562</v>
+        <v>0.0346</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7927</v>
+        <v>0.3627</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3461</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4372</v>
+        <v>1.5076</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0394</v>
+        <v>0.0385</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3978</v>
+        <v>1.4691</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0476</v>
+        <v>1.0545</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0693</v>
+        <v>-0.0689</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1169</v>
+        <v>1.1235</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1785</v>
+        <v>0.1779</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8691</v>
+        <v>0.8766</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0641</v>
+        <v>-0.0022</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U16" t="n">
-        <v>0.075</v>
+        <v>0.1372</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8083</v>
+        <v>0.7938</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5986</v>
+        <v>-1.434</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2097</v>
+        <v>2.2277</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8252</v>
+        <v>0.1094</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0145</v>
+        <v>-0.1603</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8397</v>
+        <v>0.2696</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1551</v>
+        <v>-0.1651</v>
       </c>
       <c r="K17" t="n">
-        <v>0.71</v>
+        <v>0.975</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4451</v>
+        <v>-1.1401</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3299</v>
+        <v>0.2745</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7245</v>
+        <v>-1.1353</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3946</v>
+        <v>1.4097</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.444</v>
+        <v>1.5039</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5565</v>
+        <v>0.8983</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1125</v>
+        <v>0.6055</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7071</v>
+        <v>0.7739</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7071</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>I. WASHINGTON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2436</v>
+        <v>0.7671</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5021</v>
+        <v>0.6361</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7457</v>
+        <v>0.131</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1193</v>
+        <v>1.6415</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1499</v>
+        <v>3.0938</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2692</v>
+        <v>-1.4522</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1272</v>
+        <v>1.7674</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0004</v>
+        <v>3.3095</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1276</v>
+        <v>-1.542</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2466</v>
+        <v>-0.1259</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1503</v>
+        <v>-0.2157</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3968</v>
+        <v>0.0898</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9409</v>
+        <v>0.1255</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7743</v>
+        <v>0.0068</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1666</v>
+        <v>0.1187</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7712</v>
+        <v>-0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4822</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. WASHINGTON</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.05</v>
+        <v>0.3178</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3074</v>
+        <v>0.7773</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3575</v>
+        <v>-0.4595</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6486</v>
+        <v>0.4469</v>
       </c>
       <c r="H19" t="n">
-        <v>3.104</v>
+        <v>0.402</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4554</v>
+        <v>0.0449</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7894</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3248</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5354</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1408</v>
+        <v>-0.1563</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2209</v>
+        <v>-0.2012</v>
       </c>
       <c r="O19" t="n">
-        <v>0.08</v>
+        <v>0.0449</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6986</v>
+        <v>0.2775</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3478</v>
+        <v>0.174</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3508</v>
+        <v>0.1035</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5986</v>
+        <v>-0.5879</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1887</v>
+        <v>-3.9942</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7873</v>
+        <v>3.4064</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4411</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4011</v>
+        <v>-3.153</v>
       </c>
       <c r="I20" t="n">
-        <v>0.04</v>
+        <v>2.4973</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6061</v>
+        <v>-1.6922</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6061</v>
+        <v>-2.3624</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.6703</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1649</v>
+        <v>1.0365</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.205</v>
+        <v>-0.7906</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04</v>
+        <v>1.827</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6276</v>
+        <v>1.2547</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4174</v>
+        <v>0.0229</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2102</v>
+        <v>1.2317</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.7313</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4274</v>
+        <v>-0.906</v>
       </c>
       <c r="F21" t="n">
-        <v>3.8079</v>
+        <v>0.1747</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6609</v>
+        <v>-2.1722</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.1426</v>
+        <v>-4.1984</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4817</v>
+        <v>2.0261</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6669</v>
+        <v>-2.0294</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.3386</v>
+        <v>-3.221</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6717</v>
+        <v>1.1916</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0061</v>
+        <v>-0.1428</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.9774</v>
       </c>
       <c r="O21" t="n">
-        <v>1.81</v>
+        <v>0.8345</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>1.217</v>
+        <v>2.758</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4506</v>
+        <v>2.1525</v>
       </c>
       <c r="U21" t="n">
-        <v>1.6676</v>
+        <v>0.6055</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="22">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8904</v>
+        <v>-1.5023</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0884</v>
+        <v>-0.7428</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.802</v>
+        <v>-0.7595</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2556</v>
+        <v>-1.2586</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1384</v>
+        <v>-1.1456</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9493</v>
+        <v>-0.9588</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9493</v>
+        <v>-0.9588</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3063</v>
+        <v>-0.2998</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2170,22 +2170,22 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0723</v>
+        <v>0.4588</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1391</v>
+        <v>0.2159</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2114</v>
+        <v>0.2429</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3168</v>
+        <v>-1.9331</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8724</v>
+        <v>-2.97</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5555</v>
+        <v>1.0368</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6088</v>
+        <v>-3.6044</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6017</v>
+        <v>-1.6026</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0071</v>
+        <v>-2.0018</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.0504</v>
+        <v>-3.0776</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7659</v>
+        <v>-0.7831</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5584</v>
+        <v>-0.5268</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2773</v>
+        <v>0.2926</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0139</v>
+        <v>1.4028</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1512</v>
+        <v>0.7984</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1651</v>
+        <v>0.6044</v>
       </c>
       <c r="V23" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W23" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.773</v>
+        <v>9.365100000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8697999999999997</v>
+        <v>-1.1459</v>
       </c>
       <c r="F24" t="n">
-        <v>8.6426</v>
+        <v>10.5108</v>
       </c>
       <c r="G24" t="n">
-        <v>3.767500000000001</v>
+        <v>3.750200000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.2166</v>
+        <v>-3.2985</v>
       </c>
       <c r="I24" t="n">
-        <v>6.9841</v>
+        <v>7.048700000000002</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2391</v>
+        <v>3.0074</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6393</v>
+        <v>3.456499999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4002000000000003</v>
+        <v>-0.4490000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5288999999999999</v>
+        <v>0.743</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.855799999999999</v>
+        <v>-6.755</v>
       </c>
       <c r="O24" t="n">
-        <v>7.3843</v>
+        <v>7.4977</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4024</v>
+        <v>-3.4144</v>
       </c>
       <c r="Q24" t="n">
-        <v>-15.8783</v>
+        <v>-15.9343</v>
       </c>
       <c r="R24" t="n">
-        <v>12.4759</v>
+        <v>12.5199</v>
       </c>
       <c r="S24" t="n">
-        <v>8.982700000000001</v>
+        <v>10.592</v>
       </c>
       <c r="T24" t="n">
-        <v>5.277900000000001</v>
+        <v>5.315300000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>3.704799999999999</v>
+        <v>5.2765</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.5749</v>
+        <v>-1.5628</v>
       </c>
       <c r="W24" t="n">
-        <v>6.4919</v>
+        <v>6.4653</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.066899999999999</v>
+        <v>-8.0282</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104695_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104695_W27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-6.4654</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104695_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-8.0282</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
